--- a/reporte_asistencia.xlsx
+++ b/reporte_asistencia.xlsx
@@ -450,7 +450,7 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" t="n">
         <v>5</v>
